--- a/analysis/tables/pythia-14m.xlsx
+++ b/analysis/tables/pythia-14m.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3853676153219305</v>
+        <v>0.2800338004672694</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08766525552845314</v>
+        <v>-0.04655937656078055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.385x - 0.088</t>
+          <t>y = 0.280x - 0.047</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.3745277775290248</v>
+        <v>0.3745277775290246</v>
       </c>
       <c r="H3" t="n">
         <v>0.07182983777736945</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2274847497375172</v>
+        <v>0.1662634170699778</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2977023597934774</v>
+        <v>0.2334744239064888</v>
       </c>
       <c r="K3" t="n">
         <v>0.05149094101684386</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>507840.834488432</v>
+        <v>0.2795176237497607</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08013535837177364</v>
+        <v>-0.0433746602947315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 507840.834x + 0.080</t>
+          <t>y = 0.280x - 0.043</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.496220794737644</v>
+        <v>0.3778776523422254</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06977740038161508</v>
+        <v>0.07177333980817276</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.577962088308577e-07</v>
+        <v>0.1551768354097159</v>
       </c>
       <c r="J4" t="n">
-        <v>507840.9146237904</v>
+        <v>0.2361429634550292</v>
       </c>
       <c r="K4" t="n">
         <v>0.05149094101684386</v>
